--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/00891-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/00891-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7A0930AD-CEB4-4D8D-BE7C-27432D19C806}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1C69513C-ECFC-4AAF-9504-27108CDC9E23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{C89C9092-7057-4F40-A40C-FB2E4C597C67}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{1A3730C3-1669-437A-839F-A144C345C0B4}"/>
   </bookViews>
   <sheets>
     <sheet name="00891-dividend-20260225_0_4" sheetId="2" r:id="rId1"/>
@@ -1561,20 +1561,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD93E071-6D2B-48AB-BE4C-768EE889444A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBCAF0F4-8A38-4465-A196-BEA82944BDEE}">
   <dimension ref="A1:R30"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.77734375" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="11" customWidth="1"/>
+    <col min="3" max="3" width="10.75" customWidth="1"/>
+    <col min="4" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="10.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1602,7 +1602,7 @@
       <c r="Q1" s="32"/>
       <c r="R1" s="24"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1632,7 +1632,7 @@
       <c r="Q2" s="34"/>
       <c r="R2" s="35"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1678,7 +1678,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1728,7 +1728,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="39">
         <v>2026</v>
       </c>
@@ -1782,7 +1782,7 @@
         <v>11.6</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="41"/>
       <c r="B6" s="42"/>
       <c r="C6" s="44"/>
@@ -1808,7 +1808,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>27</v>
       </c>
@@ -1864,7 +1864,7 @@
         <v>2.89</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="49">
         <v>2025</v>
       </c>
@@ -1918,7 +1918,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
         <v>27</v>
       </c>
@@ -1974,7 +1974,7 @@
         <v>3.14</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
         <v>27</v>
       </c>
@@ -2030,7 +2030,7 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
         <v>27</v>
       </c>
@@ -2086,7 +2086,7 @@
         <v>2.42</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
         <v>27</v>
       </c>
@@ -2142,7 +2142,7 @@
         <v>2.1800000000000002</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="51">
         <v>2024</v>
       </c>
@@ -2196,7 +2196,7 @@
         <v>8.9700000000000006</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>27</v>
       </c>
@@ -2252,7 +2252,7 @@
         <v>2.71</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>27</v>
       </c>
@@ -2308,7 +2308,7 @@
         <v>2.25</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>27</v>
       </c>
@@ -2364,7 +2364,7 @@
         <v>2.21</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>27</v>
       </c>
@@ -2420,7 +2420,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="49">
         <v>2023</v>
       </c>
@@ -2474,7 +2474,7 @@
         <v>5.32</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
         <v>27</v>
       </c>
@@ -2530,7 +2530,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="19" t="s">
         <v>27</v>
       </c>
@@ -2586,7 +2586,7 @@
         <v>1.67</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="19" t="s">
         <v>27</v>
       </c>
@@ -2642,7 +2642,7 @@
         <v>1.04</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="19" t="s">
         <v>27</v>
       </c>
@@ -2698,7 +2698,7 @@
         <v>0.87</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="51">
         <v>2022</v>
       </c>
@@ -2752,7 +2752,7 @@
         <v>4.72</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
         <v>27</v>
       </c>
@@ -2808,7 +2808,7 @@
         <v>0.84</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>27</v>
       </c>
@@ -2864,7 +2864,7 @@
         <v>2.11</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
         <v>27</v>
       </c>
@@ -2920,7 +2920,7 @@
         <v>1.77</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="49">
         <v>2021</v>
       </c>
@@ -2974,7 +2974,7 @@
         <v>3.38</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="19" t="s">
         <v>27</v>
       </c>
@@ -3030,7 +3030,7 @@
         <v>1.77</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="19" t="s">
         <v>27</v>
       </c>
@@ -3086,7 +3086,7 @@
         <v>1.61</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="51" t="s">
         <v>58</v>
       </c>
